--- a/降圧薬詳細_Ca-ARNI_薬価付き_日本語表_英語タイトル引用付き.xlsx
+++ b/降圧薬詳細_Ca-ARNI_薬価付き_日本語表_英語タイトル引用付き.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R05169daeb4024787"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R319ab3db97c14790"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -518,6 +518,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="200" formatCode="#,##0.0&quot; 円/薬価単位&quot;"/>
+    <x:numFmt numFmtId="201" formatCode="#,##0&quot; 円/年&quot;"/>
+  </x:numFmts>
   <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
@@ -563,7 +567,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top"/>
@@ -579,6 +583,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -768,9 +778,10 @@
     <x:col min="3" max="3" width="24.5" customWidth="1"/>
     <x:col min="4" max="4" width="24.6640625" customWidth="1"/>
     <x:col min="5" max="5" width="27.6640625" customWidth="1"/>
-    <x:col min="6" max="6" width="28.1640625" customWidth="1"/>
-    <x:col min="7" max="7" width="22.5" customWidth="1"/>
-    <x:col min="8" max="8" width="28.5" customWidth="1"/>
+    <x:col min="6" max="6" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32.220001220703125" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="46.66999816894531" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1672,7 +1683,7 @@
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
+    <x:row r="32" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A32" s="4" t="str">
         <x:v>ARB</x:v>
       </x:c>
@@ -1688,14 +1699,22 @@
       <x:c r="E32" s="4" t="str">
         <x:v>Neutel JM, et al. J Clin Hypertens. 2002;4:58–66.</x:v>
       </x:c>
-      <x:c r="F32" s="4" t="str"/>
-      <x:c r="G32" s="4" t="str"/>
-      <x:c r="H32" s="4" t="str"/>
+      <x:c r="F32" s="6" t="n">
+        <x:v>10.8</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="n">
+        <x:f>ROUND(ROUND(F32*365,4),0)</x:f>
+        <x:v>3942</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="str">
+        <x:v>10.8円 × 365単位/年。1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I32" s="4" t="str">
-        <x:v>20–160 mgの用量反応試験を基にした保守的なアプリ設定値。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
+        <x:v>20–160 mgの用量反応試験を基にした保守的なアプリ設定値。
+薬価: テルミサルタン２０ｍｇ錠 (２０ｍｇ１錠)、コード 2149042F1017。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A33" s="4" t="str">
         <x:v>ARB</x:v>
       </x:c>
@@ -1711,14 +1730,22 @@
       <x:c r="E33" s="4" t="str">
         <x:v>Neutel JM, et al. J Clin Hypertens. 2002;4:58–66.</x:v>
       </x:c>
-      <x:c r="F33" s="4" t="str"/>
-      <x:c r="G33" s="4" t="str"/>
-      <x:c r="H33" s="4" t="str"/>
+      <x:c r="F33" s="6" t="n">
+        <x:v>10.8</x:v>
+      </x:c>
+      <x:c r="G33" s="7" t="n">
+        <x:f>ROUND(ROUND(F33*365,4),0)</x:f>
+        <x:v>3942</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>10.8円 × 365単位/年。1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I33" s="4" t="str">
-        <x:v>20–160 mgの用量反応試験を基にした保守的なアプリ設定値。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
+        <x:v>20–160 mgの用量反応試験を基にした保守的なアプリ設定値。
+薬価: テルミサルタン４０ｍｇ錠 (４０ｍｇ１錠)、コード 2149042F2013。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A34" s="4" t="str">
         <x:v>ARB</x:v>
       </x:c>
@@ -1734,14 +1761,22 @@
       <x:c r="E34" s="4" t="str">
         <x:v>Neutel JM, et al. J Clin Hypertens. 2002;4:58–66.</x:v>
       </x:c>
-      <x:c r="F34" s="4" t="str"/>
-      <x:c r="G34" s="4" t="str"/>
-      <x:c r="H34" s="4" t="str"/>
+      <x:c r="F34" s="6" t="n">
+        <x:v>10.8</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="n">
+        <x:f>ROUND(ROUND(F34*365,4),0)</x:f>
+        <x:v>3942</x:v>
+      </x:c>
+      <x:c r="H34" s="4" t="str">
+        <x:v>10.8円 × 365単位/年。1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I34" s="4" t="str">
-        <x:v>用量範囲で報告された最大平均低下量。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
+        <x:v>用量範囲で報告された最大平均低下量。
+薬価: テルミサルタン８０ｍｇ錠 (８０ｍｇ１錠)、コード 2149042F3010。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="66" hidden="0" customHeight="1">
       <x:c r="A35" s="4" t="str">
         <x:v>ARB</x:v>
       </x:c>
@@ -1757,14 +1792,22 @@
       <x:c r="E35" s="4" t="str">
         <x:v>Reif M, et al. Clin Ther. 1998;20:100–115.</x:v>
       </x:c>
-      <x:c r="F35" s="4" t="str"/>
-      <x:c r="G35" s="4" t="str"/>
-      <x:c r="H35" s="4" t="str"/>
+      <x:c r="F35" s="6" t="n">
+        <x:v>10.8</x:v>
+      </x:c>
+      <x:c r="G35" s="7" t="n">
+        <x:f>ROUND(ROUND(F35*365,4),0)</x:f>
+        <x:v>3942</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="str">
+        <x:v>10.8円 × 365単位/年。1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I35" s="4" t="str">
-        <x:v>固定用量RCT。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
+        <x:v>固定用量RCT。
+薬価: カンデサルタンシレキセチル４ｍｇ錠 (４ｍｇ１錠)、コード 2149040F2014。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="66" hidden="0" customHeight="1">
       <x:c r="A36" s="4" t="str">
         <x:v>ARB</x:v>
       </x:c>
@@ -1780,14 +1823,22 @@
       <x:c r="E36" s="4" t="str">
         <x:v>Reif M, et al. Clin Ther. 1998;20:100–115.</x:v>
       </x:c>
-      <x:c r="F36" s="4" t="str"/>
-      <x:c r="G36" s="4" t="str"/>
-      <x:c r="H36" s="4" t="str"/>
+      <x:c r="F36" s="6" t="n">
+        <x:v>10.8</x:v>
+      </x:c>
+      <x:c r="G36" s="7" t="n">
+        <x:f>ROUND(ROUND(F36*365,4),0)</x:f>
+        <x:v>3942</x:v>
+      </x:c>
+      <x:c r="H36" s="4" t="str">
+        <x:v>10.8円 × 365単位/年。1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I36" s="4" t="str">
-        <x:v>固定用量RCT。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
+        <x:v>固定用量RCT。
+薬価: カンデサルタンシレキセチル８ｍｇ錠 (８ｍｇ１錠)、コード 2149040F3010。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="66" hidden="0" customHeight="1">
       <x:c r="A37" s="4" t="str">
         <x:v>ARB</x:v>
       </x:c>
@@ -1803,14 +1854,22 @@
       <x:c r="E37" s="4" t="str">
         <x:v>Reif M, et al. Clin Ther. 1998;20:100–115.</x:v>
       </x:c>
-      <x:c r="F37" s="4" t="str"/>
-      <x:c r="G37" s="4" t="str"/>
-      <x:c r="H37" s="4" t="str"/>
+      <x:c r="F37" s="6" t="n">
+        <x:v>13.1</x:v>
+      </x:c>
+      <x:c r="G37" s="7" t="n">
+        <x:f>ROUND(ROUND(F37*365,4),0)</x:f>
+        <x:v>4782</x:v>
+      </x:c>
+      <x:c r="H37" s="4" t="str">
+        <x:v>13.1円 × 365単位/年。1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I37" s="4" t="str">
-        <x:v>8 mgと16 mgのRCT値から補間したアプリ設定値。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
+        <x:v>8 mgと16 mgのRCT値から補間したアプリ設定値。
+薬価: カンデサルタンシレキセチル１２ｍｇ錠 (１２ｍｇ１錠)、コード 2149040F4017。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="66" hidden="0" customHeight="1">
       <x:c r="A38" s="4" t="str">
         <x:v>Ca拮抗薬</x:v>
       </x:c>
@@ -1826,14 +1885,22 @@
       <x:c r="E38" s="4" t="str">
         <x:v>Law MR, et al. BMJ. 2003;326:1427.</x:v>
       </x:c>
-      <x:c r="F38" s="4" t="str"/>
-      <x:c r="G38" s="4" t="str"/>
-      <x:c r="H38" s="4" t="str"/>
+      <x:c r="F38" s="6" t="n">
+        <x:v>9.1</x:v>
+      </x:c>
+      <x:c r="G38" s="7" t="n">
+        <x:f>ROUND(ROUND(F38*365,4),0)</x:f>
+        <x:v>3322</x:v>
+      </x:c>
+      <x:c r="H38" s="4" t="str">
+        <x:v>9.1円 × 365単位/年。CR20mg錠 1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I38" s="4" t="str">
-        <x:v>354試験メタ解析の標準量クラス平均を採用。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
+        <x:v>354試験メタ解析の標準量クラス平均を採用。
+薬価: ニフェジピンＣＲ錠２０ｍｇ「サワイ」 (２０ｍｇ１錠)、コード 2171014G4061。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="66" hidden="0" customHeight="1">
       <x:c r="A39" s="4" t="str">
         <x:v>Ca拮抗薬</x:v>
       </x:c>
@@ -1849,14 +1916,22 @@
       <x:c r="E39" s="4" t="str">
         <x:v>Law MR, et al. BMJ. 2003;326:1427.</x:v>
       </x:c>
-      <x:c r="F39" s="4" t="str"/>
-      <x:c r="G39" s="4" t="str"/>
-      <x:c r="H39" s="4" t="str"/>
+      <x:c r="F39" s="6" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G39" s="7" t="n">
+        <x:f>ROUND(ROUND(F39*365,4),0)</x:f>
+        <x:v>6205</x:v>
+      </x:c>
+      <x:c r="H39" s="4" t="str">
+        <x:v>17円 × 365単位/年。CR40mg錠 1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I39" s="4" t="str">
-        <x:v>標準量クラス平均からの保守的な用量反応設定。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
+        <x:v>標準量クラス平均からの保守的な用量反応設定。
+薬価: ニフェジピンＣＲ錠４０ｍｇ「サワイ」 (４０ｍｇ１錠)、コード 2171014G5068。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A40" s="4" t="str">
         <x:v>Ca拮抗薬</x:v>
       </x:c>
@@ -1872,14 +1947,22 @@
       <x:c r="E40" s="4" t="str">
         <x:v>Law MR, et al. BMJ. 2003;326:1427.</x:v>
       </x:c>
-      <x:c r="F40" s="4" t="str"/>
-      <x:c r="G40" s="4" t="str"/>
-      <x:c r="H40" s="4" t="str"/>
+      <x:c r="F40" s="6" t="n">
+        <x:v>12.2</x:v>
+      </x:c>
+      <x:c r="G40" s="7" t="n">
+        <x:f>ROUND(ROUND(F40*365,4),0)</x:f>
+        <x:v>4453</x:v>
+      </x:c>
+      <x:c r="H40" s="4" t="str">
+        <x:v>12.2円 × 365単位/年。1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I40" s="4" t="str">
-        <x:v>354試験メタ解析の標準量クラス平均を採用。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
+        <x:v>354試験メタ解析の標準量クラス平均を採用。
+薬価: シルニジピン１０ｍｇ錠 (１０ｍｇ１錠)、コード 2149037F2012。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A41" s="4" t="str">
         <x:v>Ca拮抗薬</x:v>
       </x:c>
@@ -1895,14 +1978,22 @@
       <x:c r="E41" s="4" t="str">
         <x:v>Law MR, et al. BMJ. 2003;326:1427.</x:v>
       </x:c>
-      <x:c r="F41" s="4" t="str"/>
-      <x:c r="G41" s="4" t="str"/>
-      <x:c r="H41" s="4" t="str"/>
+      <x:c r="F41" s="6" t="n">
+        <x:v>18.9</x:v>
+      </x:c>
+      <x:c r="G41" s="7" t="n">
+        <x:f>ROUND(ROUND(F41*365,4),0)</x:f>
+        <x:v>6899</x:v>
+      </x:c>
+      <x:c r="H41" s="4" t="str">
+        <x:v>18.9円 × 365単位/年。1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I41" s="4" t="str">
-        <x:v>標準量クラス平均からの保守的な用量反応設定。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
+        <x:v>標準量クラス平均からの保守的な用量反応設定。
+薬価: シルニジピン２０ｍｇ錠 (２０ｍｇ１錠)、コード 2149037F3019。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="66" hidden="0" customHeight="1">
       <x:c r="A42" s="4" t="str">
         <x:v>サイアザイド系利尿薬</x:v>
       </x:c>
@@ -1918,14 +2009,22 @@
       <x:c r="E42" s="4" t="str">
         <x:v>Law MR, et al. BMJ. 2003;326:1427.</x:v>
       </x:c>
-      <x:c r="F42" s="4" t="str"/>
-      <x:c r="G42" s="4" t="str"/>
-      <x:c r="H42" s="4" t="str"/>
+      <x:c r="F42" s="6" t="n">
+        <x:v>6.3</x:v>
+      </x:c>
+      <x:c r="G42" s="7" t="n">
+        <x:f>ROUND(ROUND(F42*365,4),0)</x:f>
+        <x:v>2300</x:v>
+      </x:c>
+      <x:c r="H42" s="4" t="str">
+        <x:v>6.3円 × 365単位/年。12.5mg錠 1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I42" s="4" t="str">
-        <x:v>低用量サイアザイドのメタ解析を基に設定。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
+        <x:v>低用量サイアザイドのメタ解析を基に設定。
+薬価: ヒドロクロロチアジド錠１２．５ｍｇ「トーワ」 (１２．５ｍｇ１錠)、コード 2132004F2037。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="66" hidden="0" customHeight="1">
       <x:c r="A43" s="4" t="str">
         <x:v>サイアザイド系利尿薬</x:v>
       </x:c>
@@ -1941,14 +2040,22 @@
       <x:c r="E43" s="4" t="str">
         <x:v>Law MR, et al. BMJ. 2003;326:1427.</x:v>
       </x:c>
-      <x:c r="F43" s="4" t="str"/>
-      <x:c r="G43" s="4" t="str"/>
-      <x:c r="H43" s="4" t="str"/>
+      <x:c r="F43" s="6" t="n">
+        <x:v>6.3</x:v>
+      </x:c>
+      <x:c r="G43" s="7" t="n">
+        <x:f>ROUND(ROUND(F43*365,4),0)</x:f>
+        <x:v>2300</x:v>
+      </x:c>
+      <x:c r="H43" s="4" t="str">
+        <x:v>6.3円 × 365単位/年。25mg錠 1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I43" s="4" t="str">
-        <x:v>低用量サイアザイドのメタ解析を基に設定。薬価は未登録。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
+        <x:v>低用量サイアザイドのメタ解析を基に設定。
+薬価: ヒドロクロロチアジド錠２５ｍｇ「トーワ」 (２５ｍｇ１錠)、コード 2132004F1103。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A44" s="4" t="str">
         <x:v>ステロイド型MRA</x:v>
       </x:c>
@@ -1964,11 +2071,19 @@
       <x:c r="E44" s="4" t="str">
         <x:v>Williams B, et al. Lancet. 2015;386:2059–2068.</x:v>
       </x:c>
-      <x:c r="F44" s="4" t="str"/>
-      <x:c r="G44" s="4" t="str"/>
-      <x:c r="H44" s="4" t="str"/>
+      <x:c r="F44" s="6" t="n">
+        <x:v>10.8</x:v>
+      </x:c>
+      <x:c r="G44" s="7" t="n">
+        <x:f>ROUND(ROUND(F44*365,4),0)</x:f>
+        <x:v>3942</x:v>
+      </x:c>
+      <x:c r="H44" s="4" t="str">
+        <x:v>10.8円 × 365単位/年。1錠/日 × 365日</x:v>
+      </x:c>
       <x:c r="I44" s="4" t="str">
-        <x:v>PATHWAY-2の25–50 mg交差試験。治療抵抗性高血圧の値。薬価は未登録。</x:v>
+        <x:v>PATHWAY-2の25–50 mg交差試験。治療抵抗性高血圧の値。
+薬価: スピロノラクトン２５ｍｇ錠 (２５ｍｇ１錠)、コード 2133001F1018。厚労省2026-08-13適用、2026-09-26確認。https://www.mhlw.go.jp/topics/2026/04/tp20260401-01.html</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
